--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/103.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/103.xlsx
@@ -426,13 +426,13 @@
         <v>-6.748252475784819</v>
       </c>
       <c r="E2">
-        <v>-8.853653308421972</v>
+        <v>-8.513401885381651</v>
       </c>
       <c r="F2">
-        <v>-0.7492986329482374</v>
+        <v>-1.044497456321362</v>
       </c>
       <c r="G2">
-        <v>-15.91042342258595</v>
+        <v>-15.06496306058472</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.246810203468243</v>
       </c>
       <c r="E3">
-        <v>-9.226536915161564</v>
+        <v>-8.146106415567525</v>
       </c>
       <c r="F3">
-        <v>-0.4068998303243134</v>
+        <v>-1.059001826947914</v>
       </c>
       <c r="G3">
-        <v>-16.10126313074278</v>
+        <v>-15.28114996066298</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.604514765257265</v>
       </c>
       <c r="E4">
-        <v>-10.27150493480154</v>
+        <v>-11.00262253486591</v>
       </c>
       <c r="F4">
-        <v>-0.4548813684443824</v>
+        <v>-0.8659963788862662</v>
       </c>
       <c r="G4">
-        <v>-15.06062128010996</v>
+        <v>-14.17644077748142</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.894176121448591</v>
       </c>
       <c r="E5">
-        <v>-10.55001061474727</v>
+        <v>-10.67716563640865</v>
       </c>
       <c r="F5">
-        <v>-0.4345616296963365</v>
+        <v>-0.5036626780517482</v>
       </c>
       <c r="G5">
-        <v>-14.87237538438316</v>
+        <v>-13.37149321651702</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.126436011891542</v>
       </c>
       <c r="E6">
-        <v>-11.37191053324341</v>
+        <v>-11.02594417600541</v>
       </c>
       <c r="F6">
-        <v>-0.1428342896898554</v>
+        <v>-0.533757841562844</v>
       </c>
       <c r="G6">
-        <v>-14.19943417152442</v>
+        <v>-13.28007250145004</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-3.337432946468768</v>
       </c>
       <c r="E7">
-        <v>-11.54844403548442</v>
+        <v>-11.71981507735669</v>
       </c>
       <c r="F7">
-        <v>-0.06063757711967493</v>
+        <v>-0.4546873644697411</v>
       </c>
       <c r="G7">
-        <v>-14.03748559428882</v>
+        <v>-13.75525165542933</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.548324083536841</v>
       </c>
       <c r="E8">
-        <v>-12.59753296647138</v>
+        <v>-12.7665718442297</v>
       </c>
       <c r="F8">
-        <v>-0.1633361546181768</v>
+        <v>-0.3216204341897301</v>
       </c>
       <c r="G8">
-        <v>-13.88590564568221</v>
+        <v>-13.35306340949989</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.777970268977572</v>
       </c>
       <c r="E9">
-        <v>-14.13862701296969</v>
+        <v>-12.76733715633699</v>
       </c>
       <c r="F9">
-        <v>-0.1084995454431282</v>
+        <v>0.2592037102976873</v>
       </c>
       <c r="G9">
-        <v>-13.50031481981391</v>
+        <v>-12.08417434138926</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.023866087123399</v>
       </c>
       <c r="E10">
-        <v>-14.81626786347748</v>
+        <v>-12.6545192833839</v>
       </c>
       <c r="F10">
-        <v>0.1084776672075687</v>
+        <v>0.2599939795494915</v>
       </c>
       <c r="G10">
-        <v>-12.37691264124485</v>
+        <v>-11.07986076223163</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.2829002033972105</v>
       </c>
       <c r="E11">
-        <v>-14.8854720032627</v>
+        <v>-15.08758232669904</v>
       </c>
       <c r="F11">
-        <v>0.2034200449852059</v>
+        <v>0.3329204695436472</v>
       </c>
       <c r="G11">
-        <v>-12.28705781421795</v>
+        <v>-11.62259821903083</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.455252197234894</v>
       </c>
       <c r="E12">
-        <v>-15.09749062782782</v>
+        <v>-15.01457879722139</v>
       </c>
       <c r="F12">
-        <v>0.3648582748873568</v>
+        <v>0.379780743875585</v>
       </c>
       <c r="G12">
-        <v>-11.58322921147782</v>
+        <v>-10.89705574809862</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>1.20797452137688</v>
       </c>
       <c r="E13">
-        <v>-15.62212792703846</v>
+        <v>-14.8672267814858</v>
       </c>
       <c r="F13">
-        <v>0.5713854040550266</v>
+        <v>0.5645580478535671</v>
       </c>
       <c r="G13">
-        <v>-10.89096434430636</v>
+        <v>-10.69783373863636</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.989112513948756</v>
       </c>
       <c r="E14">
-        <v>-17.72713925628994</v>
+        <v>-17.78991749145827</v>
       </c>
       <c r="F14">
-        <v>0.5685426519368127</v>
+        <v>0.6161963629323858</v>
       </c>
       <c r="G14">
-        <v>-10.92084201779828</v>
+        <v>-9.877030319811617</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>2.8069161764635</v>
       </c>
       <c r="E15">
-        <v>-17.8297273064597</v>
+        <v>-17.77349271623245</v>
       </c>
       <c r="F15">
-        <v>0.5904389699236786</v>
+        <v>0.6981246373498993</v>
       </c>
       <c r="G15">
-        <v>-9.980700053373894</v>
+        <v>-8.746594887244381</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>3.660304706788525</v>
       </c>
       <c r="E16">
-        <v>-18.89809847977132</v>
+        <v>-17.9684661646327</v>
       </c>
       <c r="F16">
-        <v>1.07310818918399</v>
+        <v>0.8604259869759647</v>
       </c>
       <c r="G16">
-        <v>-9.5241592707807</v>
+        <v>-8.450228229477746</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>4.533691141558885</v>
       </c>
       <c r="E17">
-        <v>-19.36065040033679</v>
+        <v>-19.76281512000998</v>
       </c>
       <c r="F17">
-        <v>0.8848752388985189</v>
+        <v>0.9403508734104473</v>
       </c>
       <c r="G17">
-        <v>-9.140947071882366</v>
+        <v>-8.299472606710415</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>5.39377222419093</v>
       </c>
       <c r="E18">
-        <v>-20.62836952794006</v>
+        <v>-20.68380710674196</v>
       </c>
       <c r="F18">
-        <v>1.049859386345339</v>
+        <v>1.13554579490019</v>
       </c>
       <c r="G18">
-        <v>-8.591340233089181</v>
+        <v>-8.442465000188156</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>6.198957393365136</v>
       </c>
       <c r="E19">
-        <v>-21.42682100802448</v>
+        <v>-20.70010055622156</v>
       </c>
       <c r="F19">
-        <v>1.147247797909372</v>
+        <v>1.872990535894992</v>
       </c>
       <c r="G19">
-        <v>-8.126046368090154</v>
+        <v>-7.779501771584785</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.909869444056643</v>
       </c>
       <c r="E20">
-        <v>-21.34174456684238</v>
+        <v>-21.82276360441113</v>
       </c>
       <c r="F20">
-        <v>1.583858098030958</v>
+        <v>2.021907986829678</v>
       </c>
       <c r="G20">
-        <v>-8.184719166682656</v>
+        <v>-7.467817219607943</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>7.485729834690562</v>
       </c>
       <c r="E21">
-        <v>-22.1106794533448</v>
+        <v>-21.12412874840378</v>
       </c>
       <c r="F21">
-        <v>1.362891530179269</v>
+        <v>1.860148264626693</v>
       </c>
       <c r="G21">
-        <v>-7.950670218147263</v>
+        <v>-7.032960510296975</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.892552177077324</v>
       </c>
       <c r="E22">
-        <v>-23.3692601204006</v>
+        <v>-22.54989161887475</v>
       </c>
       <c r="F22">
-        <v>1.750875723873202</v>
+        <v>2.024221781172135</v>
       </c>
       <c r="G22">
-        <v>-7.376644795456414</v>
+        <v>-6.690828870995456</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>8.111174444516863</v>
       </c>
       <c r="E23">
-        <v>-22.43658919920283</v>
+        <v>-22.89936754346869</v>
       </c>
       <c r="F23">
-        <v>1.593127528754025</v>
+        <v>1.743573255897111</v>
       </c>
       <c r="G23">
-        <v>-7.316982143747668</v>
+        <v>-6.426385803864012</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>8.137581609905308</v>
       </c>
       <c r="E24">
-        <v>-22.24417433861692</v>
+        <v>-22.15220555999514</v>
       </c>
       <c r="F24">
-        <v>1.597096295778116</v>
+        <v>1.539881752171035</v>
       </c>
       <c r="G24">
-        <v>-6.830249185836323</v>
+        <v>-6.625243653316954</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.983140429340257</v>
       </c>
       <c r="E25">
-        <v>-22.54188074835518</v>
+        <v>-23.07442929165721</v>
       </c>
       <c r="F25">
-        <v>1.685733148453431</v>
+        <v>2.136864448113681</v>
       </c>
       <c r="G25">
-        <v>-7.212438426163024</v>
+        <v>-6.94454577057966</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.672058375014664</v>
       </c>
       <c r="E26">
-        <v>-22.83217404614288</v>
+        <v>-24.06957504026479</v>
       </c>
       <c r="F26">
-        <v>1.485818783335679</v>
+        <v>1.560409748246961</v>
       </c>
       <c r="G26">
-        <v>-7.30666317330176</v>
+        <v>-5.963538432018508</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.240508989884362</v>
       </c>
       <c r="E27">
-        <v>-23.34220248820477</v>
+        <v>-22.61235286086254</v>
       </c>
       <c r="F27">
-        <v>1.349711929550982</v>
+        <v>1.513604903622064</v>
       </c>
       <c r="G27">
-        <v>-6.570109827905932</v>
+        <v>-6.514264235203966</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.727625982796964</v>
       </c>
       <c r="E28">
-        <v>-22.66358801578533</v>
+        <v>-23.8481236043417</v>
       </c>
       <c r="F28">
-        <v>1.539053473977261</v>
+        <v>1.510625952795122</v>
       </c>
       <c r="G28">
-        <v>-7.106269230718596</v>
+        <v>-6.082125483780741</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.166854302725926</v>
       </c>
       <c r="E29">
-        <v>-22.79058906933044</v>
+        <v>-22.46262339627293</v>
       </c>
       <c r="F29">
-        <v>1.186596555084381</v>
+        <v>1.642667433494886</v>
       </c>
       <c r="G29">
-        <v>-7.425303193792621</v>
+        <v>-6.856342905776858</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.584490862758659</v>
       </c>
       <c r="E30">
-        <v>-22.91064344374779</v>
+        <v>-22.94861922677611</v>
       </c>
       <c r="F30">
-        <v>1.664763298427097</v>
+        <v>1.704726533497297</v>
       </c>
       <c r="G30">
-        <v>-7.015815194949091</v>
+        <v>-6.294947214318328</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>4.997056140252606</v>
       </c>
       <c r="E31">
-        <v>-23.14604257961451</v>
+        <v>-23.99450199816564</v>
       </c>
       <c r="F31">
-        <v>1.515312138598908</v>
+        <v>1.645575117555633</v>
       </c>
       <c r="G31">
-        <v>-6.575777481869164</v>
+        <v>-7.381898631227237</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.408296035153026</v>
       </c>
       <c r="E32">
-        <v>-23.08136691383696</v>
+        <v>-21.90030466484447</v>
       </c>
       <c r="F32">
-        <v>1.236624241247197</v>
+        <v>1.196931819888539</v>
       </c>
       <c r="G32">
-        <v>-7.562005550745747</v>
+        <v>-6.140838008919715</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>3.812494841760089</v>
       </c>
       <c r="E33">
-        <v>-21.93770986014783</v>
+        <v>-22.39645786254686</v>
       </c>
       <c r="F33">
-        <v>1.108909445108414</v>
+        <v>1.601421396633181</v>
       </c>
       <c r="G33">
-        <v>-7.311940182891359</v>
+        <v>-6.557913778139256</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.206208939971655</v>
       </c>
       <c r="E34">
-        <v>-21.89738379910952</v>
+        <v>-20.72470375550523</v>
       </c>
       <c r="F34">
-        <v>1.163281236597281</v>
+        <v>1.493165595077403</v>
       </c>
       <c r="G34">
-        <v>-7.274100647377489</v>
+        <v>-6.511211912216758</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>2.588505929895479</v>
       </c>
       <c r="E35">
-        <v>-20.29961590040521</v>
+        <v>-20.29179522579397</v>
       </c>
       <c r="F35">
-        <v>1.401476941103036</v>
+        <v>1.47994956921306</v>
       </c>
       <c r="G35">
-        <v>-6.678871180507608</v>
+        <v>-7.170321665812415</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.961647748031583</v>
       </c>
       <c r="E36">
-        <v>-21.03245884906651</v>
+        <v>-20.65247459508289</v>
       </c>
       <c r="F36">
-        <v>1.080779660638379</v>
+        <v>1.562528746761819</v>
       </c>
       <c r="G36">
-        <v>-7.488253217221864</v>
+        <v>-6.829269264356698</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.340779882362899</v>
       </c>
       <c r="E37">
-        <v>-20.62023638862228</v>
+        <v>-19.18534411455185</v>
       </c>
       <c r="F37">
-        <v>1.412249308739855</v>
+        <v>1.499148836025933</v>
       </c>
       <c r="G37">
-        <v>-7.453459383604123</v>
+        <v>-6.689166977134741</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.7460993712447528</v>
       </c>
       <c r="E38">
-        <v>-19.40600759599761</v>
+        <v>-18.9086588811572</v>
       </c>
       <c r="F38">
-        <v>1.501750864845</v>
+        <v>1.557552742775509</v>
       </c>
       <c r="G38">
-        <v>-7.452466219942342</v>
+        <v>-7.19742179159689</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.196291866187538</v>
       </c>
       <c r="E39">
-        <v>-18.89122425622767</v>
+        <v>-19.06364590406972</v>
       </c>
       <c r="F39">
-        <v>1.403844581446618</v>
+        <v>2.009290601801372</v>
       </c>
       <c r="G39">
-        <v>-7.12705614615968</v>
+        <v>-7.156513380368116</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.2913254278397633</v>
       </c>
       <c r="E40">
-        <v>-17.8784899145743</v>
+        <v>-17.70144469477042</v>
       </c>
       <c r="F40">
-        <v>1.209848525334863</v>
+        <v>1.599699908303099</v>
       </c>
       <c r="G40">
-        <v>-7.420334064938176</v>
+        <v>-6.830507408388385</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.7096779911998612</v>
       </c>
       <c r="E41">
-        <v>-17.52366133370328</v>
+        <v>-18.37292229215377</v>
       </c>
       <c r="F41">
-        <v>1.826880938166972</v>
+        <v>2.003196501438761</v>
       </c>
       <c r="G41">
-        <v>-7.395011702108291</v>
+        <v>-7.720468123528502</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.061613583521564</v>
       </c>
       <c r="E42">
-        <v>-18.29555331373272</v>
+        <v>-18.78194312147457</v>
       </c>
       <c r="F42">
-        <v>1.660533219926959</v>
+        <v>1.618861166174001</v>
       </c>
       <c r="G42">
-        <v>-7.844371911426804</v>
+        <v>-6.8011892170926</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.35576974731107</v>
       </c>
       <c r="E43">
-        <v>-17.18361822046732</v>
+        <v>-17.27031585534417</v>
       </c>
       <c r="F43">
-        <v>1.744616918095385</v>
+        <v>1.916558285628731</v>
       </c>
       <c r="G43">
-        <v>-7.982676572420937</v>
+        <v>-7.704054438744795</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.602343524633685</v>
       </c>
       <c r="E44">
-        <v>-16.28854269048123</v>
+        <v>-16.62663403141989</v>
       </c>
       <c r="F44">
-        <v>2.045042762842418</v>
+        <v>1.683069355103662</v>
       </c>
       <c r="G44">
-        <v>-8.145237600581309</v>
+        <v>-7.370086604743117</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.812113464013932</v>
       </c>
       <c r="E45">
-        <v>-16.59728951985019</v>
+        <v>-16.5769838423998</v>
       </c>
       <c r="F45">
-        <v>1.557188490414958</v>
+        <v>1.752605130732862</v>
       </c>
       <c r="G45">
-        <v>-8.394568027325979</v>
+        <v>-7.398087198914274</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.996625262116527</v>
       </c>
       <c r="E46">
-        <v>-15.22863070661595</v>
+        <v>-15.91104456872782</v>
       </c>
       <c r="F46">
-        <v>1.587264649455068</v>
+        <v>1.467352772361655</v>
       </c>
       <c r="G46">
-        <v>-8.244841984221361</v>
+        <v>-7.679099546469769</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.163699448001319</v>
       </c>
       <c r="E47">
-        <v>-15.22745330337395</v>
+        <v>-15.1783601166568</v>
       </c>
       <c r="F47">
-        <v>1.768757347364429</v>
+        <v>1.74005584505892</v>
       </c>
       <c r="G47">
-        <v>-8.440518399411063</v>
+        <v>-8.141797943766006</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.319851109932967</v>
       </c>
       <c r="E48">
-        <v>-13.9093232031173</v>
+        <v>-14.27292796661517</v>
       </c>
       <c r="F48">
-        <v>2.044610411127503</v>
+        <v>1.603443789087198</v>
       </c>
       <c r="G48">
-        <v>-8.311208490647131</v>
+        <v>-8.201321552562103</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.472822962284644</v>
       </c>
       <c r="E49">
-        <v>-13.29489532128257</v>
+        <v>-13.84084361917331</v>
       </c>
       <c r="F49">
-        <v>1.883911771887862</v>
+        <v>1.644216297880186</v>
       </c>
       <c r="G49">
-        <v>-8.94210246461158</v>
+        <v>-8.062387887915508</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.629111324899375</v>
       </c>
       <c r="E50">
-        <v>-13.37799734779733</v>
+        <v>-13.28541722518452</v>
       </c>
       <c r="F50">
-        <v>1.759076153103348</v>
+        <v>1.873647773849899</v>
       </c>
       <c r="G50">
-        <v>-9.13333612768758</v>
+        <v>-8.593502019326325</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.79348781112213</v>
       </c>
       <c r="E51">
-        <v>-13.08855993159708</v>
+        <v>-13.8031757723775</v>
       </c>
       <c r="F51">
-        <v>1.867567926840527</v>
+        <v>1.761285422855386</v>
       </c>
       <c r="G51">
-        <v>-9.047705556768792</v>
+        <v>-7.661275569286333</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.968658627070487</v>
       </c>
       <c r="E52">
-        <v>-12.78308266046166</v>
+        <v>-13.88230632718754</v>
       </c>
       <c r="F52">
-        <v>1.364098314086834</v>
+        <v>1.518020275714309</v>
       </c>
       <c r="G52">
-        <v>-9.367517498044545</v>
+        <v>-8.330773814784223</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.15484391651343</v>
       </c>
       <c r="E53">
-        <v>-12.59014249689086</v>
+        <v>-13.88127836358779</v>
       </c>
       <c r="F53">
-        <v>1.789629007624005</v>
+        <v>1.47971359703166</v>
       </c>
       <c r="G53">
-        <v>-8.989787562559242</v>
+        <v>-7.761075275113202</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.346509942262414</v>
       </c>
       <c r="E54">
-        <v>-11.23045459066581</v>
+        <v>-11.98260695249581</v>
       </c>
       <c r="F54">
-        <v>1.79357560276528</v>
+        <v>1.447679977480066</v>
       </c>
       <c r="G54">
-        <v>-8.833241795643726</v>
+        <v>-8.988340854158581</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.533882646068203</v>
       </c>
       <c r="E55">
-        <v>-11.40803869887661</v>
+        <v>-12.09047973183253</v>
       </c>
       <c r="F55">
-        <v>1.467732861781361</v>
+        <v>1.832607618757201</v>
       </c>
       <c r="G55">
-        <v>-9.357420334149769</v>
+        <v>-7.911658749512491</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.70900788060923</v>
       </c>
       <c r="E56">
-        <v>-11.29188334057986</v>
+        <v>-11.29724052533093</v>
       </c>
       <c r="F56">
-        <v>1.597918239148229</v>
+        <v>1.386284450256225</v>
       </c>
       <c r="G56">
-        <v>-9.59993103708354</v>
+        <v>-8.722268998621816</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.863049729052805</v>
       </c>
       <c r="E57">
-        <v>-10.47052231049063</v>
+        <v>-10.61865322375554</v>
       </c>
       <c r="F57">
-        <v>1.963785979733051</v>
+        <v>1.558387355792945</v>
       </c>
       <c r="G57">
-        <v>-9.734143863791132</v>
+        <v>-8.800205861707338</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.987849338081298</v>
       </c>
       <c r="E58">
-        <v>-10.55807129848093</v>
+        <v>-11.09564191945747</v>
       </c>
       <c r="F58">
-        <v>1.623395316209904</v>
+        <v>1.786719739857343</v>
       </c>
       <c r="G58">
-        <v>-10.03886964904443</v>
+        <v>-7.635691673358845</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.080600366914669</v>
       </c>
       <c r="E59">
-        <v>-10.51400471791228</v>
+        <v>-9.054056397157416</v>
       </c>
       <c r="F59">
-        <v>1.61757994808841</v>
+        <v>1.326661089951761</v>
       </c>
       <c r="G59">
-        <v>-8.895549573238348</v>
+        <v>-9.795259844991618</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.140729507196691</v>
       </c>
       <c r="E60">
-        <v>-10.7651629433257</v>
+        <v>-10.22218985285801</v>
       </c>
       <c r="F60">
-        <v>1.295412988534225</v>
+        <v>1.388910234664024</v>
       </c>
       <c r="G60">
-        <v>-9.49109685248</v>
+        <v>-9.095738261998077</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.168312713022344</v>
       </c>
       <c r="E61">
-        <v>-10.25248081549531</v>
+        <v>-8.727874942858927</v>
       </c>
       <c r="F61">
-        <v>1.848563455855254</v>
+        <v>1.509930705898245</v>
       </c>
       <c r="G61">
-        <v>-10.03769109483245</v>
+        <v>-8.6004210595034</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.166066617829159</v>
       </c>
       <c r="E62">
-        <v>-9.459046884611391</v>
+        <v>-9.405751274015119</v>
       </c>
       <c r="F62">
-        <v>1.655364003818965</v>
+        <v>1.544065903199626</v>
       </c>
       <c r="G62">
-        <v>-9.763975189645505</v>
+        <v>-9.036684750668558</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.13912029292457</v>
       </c>
       <c r="E63">
-        <v>-9.244084751941287</v>
+        <v>-11.29658389659982</v>
       </c>
       <c r="F63">
-        <v>1.334869437711484</v>
+        <v>1.165568107939176</v>
       </c>
       <c r="G63">
-        <v>-9.876689333621071</v>
+        <v>-10.16163460927722</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.089974632950742</v>
       </c>
       <c r="E64">
-        <v>-9.061089117291328</v>
+        <v>-8.408558655156067</v>
       </c>
       <c r="F64">
-        <v>1.504675969670817</v>
+        <v>1.400876716561084</v>
       </c>
       <c r="G64">
-        <v>-10.48363151060889</v>
+        <v>-7.896926821862735</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.019350794634099</v>
       </c>
       <c r="E65">
-        <v>-8.826165471195413</v>
+        <v>-9.464372370044412</v>
       </c>
       <c r="F65">
-        <v>1.523686775479752</v>
+        <v>0.9680720617542994</v>
       </c>
       <c r="G65">
-        <v>-10.32417246361882</v>
+        <v>-9.238061925276885</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.930756397288129</v>
       </c>
       <c r="E66">
-        <v>-8.714325748627978</v>
+        <v>-9.845081179869258</v>
       </c>
       <c r="F66">
-        <v>1.176292964398532</v>
+        <v>0.9623580508113938</v>
       </c>
       <c r="G66">
-        <v>-9.909910658107659</v>
+        <v>-9.62814019562367</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.825986909476192</v>
       </c>
       <c r="E67">
-        <v>-9.568364247156554</v>
+        <v>-8.574192120460619</v>
       </c>
       <c r="F67">
-        <v>1.446780432520097</v>
+        <v>0.943470774063863</v>
       </c>
       <c r="G67">
-        <v>-10.52603297787588</v>
+        <v>-8.803509786155532</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.704576453861366</v>
       </c>
       <c r="E68">
-        <v>-8.536315963860464</v>
+        <v>-8.469022840106483</v>
       </c>
       <c r="F68">
-        <v>0.7866173727869092</v>
+        <v>0.843287121559079</v>
       </c>
       <c r="G68">
-        <v>-10.35992635544295</v>
+        <v>-8.814888131174007</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.567817029626301</v>
       </c>
       <c r="E69">
-        <v>-9.320534450138778</v>
+        <v>-8.885008462451081</v>
       </c>
       <c r="F69">
-        <v>0.9331180884946353</v>
+        <v>1.043960081810327</v>
       </c>
       <c r="G69">
-        <v>-9.746574962291096</v>
+        <v>-9.299753941401203</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.417316863697105</v>
       </c>
       <c r="E70">
-        <v>-8.80875348863592</v>
+        <v>-8.969111281721535</v>
       </c>
       <c r="F70">
-        <v>1.09902078537241</v>
+        <v>0.6883769274403695</v>
       </c>
       <c r="G70">
-        <v>-10.46422509265769</v>
+        <v>-9.191985752461308</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.253578593650622</v>
       </c>
       <c r="E71">
-        <v>-8.756395272159235</v>
+        <v>-9.77700463011195</v>
       </c>
       <c r="F71">
-        <v>0.8883293015000924</v>
+        <v>1.059095559244182</v>
       </c>
       <c r="G71">
-        <v>-9.671756633103568</v>
+        <v>-9.546618011719117</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.076524220222005</v>
       </c>
       <c r="E72">
-        <v>-9.464164060240059</v>
+        <v>-8.779196138787855</v>
       </c>
       <c r="F72">
-        <v>0.9476517576806232</v>
+        <v>0.7842766554438897</v>
       </c>
       <c r="G72">
-        <v>-10.36316737952589</v>
+        <v>-8.786043347890336</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.886497212212162</v>
       </c>
       <c r="E73">
-        <v>-8.937276109447613</v>
+        <v>-9.392722854295052</v>
       </c>
       <c r="F73">
-        <v>0.884479312419659</v>
+        <v>0.5972615750073917</v>
       </c>
       <c r="G73">
-        <v>-9.819526143794477</v>
+        <v>-9.28573378104239</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-2.68166532875266</v>
       </c>
       <c r="E74">
-        <v>-9.55635926256222</v>
+        <v>-10.1574779592884</v>
       </c>
       <c r="F74">
-        <v>0.8661479164484475</v>
+        <v>0.7034680611085919</v>
       </c>
       <c r="G74">
-        <v>-9.883667963617855</v>
+        <v>-8.85806426609718</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.457901846344181</v>
       </c>
       <c r="E75">
-        <v>-9.936329931123815</v>
+        <v>-9.980958042469407</v>
       </c>
       <c r="F75">
-        <v>0.6121199039060446</v>
+        <v>0.582933787590411</v>
       </c>
       <c r="G75">
-        <v>-9.622376535839798</v>
+        <v>-8.026925324098835</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.213016895261596</v>
       </c>
       <c r="E76">
-        <v>-10.38025623809574</v>
+        <v>-9.89466344177924</v>
       </c>
       <c r="F76">
-        <v>0.6135959178192342</v>
+        <v>0.3450690776209832</v>
       </c>
       <c r="G76">
-        <v>-9.223780231820468</v>
+        <v>-8.164869135629187</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.942890947947187</v>
       </c>
       <c r="E77">
-        <v>-10.78996539546571</v>
+        <v>-11.18955794190254</v>
       </c>
       <c r="F77">
-        <v>0.4212025720939038</v>
+        <v>0.7342933130467053</v>
       </c>
       <c r="G77">
-        <v>-9.130906187261756</v>
+        <v>-8.063493610125626</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-1.641779263845573</v>
       </c>
       <c r="E78">
-        <v>-10.58832150485216</v>
+        <v>-11.46732095211102</v>
       </c>
       <c r="F78">
-        <v>0.5723467135456983</v>
+        <v>0.3015377531232991</v>
       </c>
       <c r="G78">
-        <v>-9.027408602067521</v>
+        <v>-8.368431270293433</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.306513051183934</v>
       </c>
       <c r="E79">
-        <v>-11.29021686214504</v>
+        <v>-11.74209064100043</v>
       </c>
       <c r="F79">
-        <v>0.42002667045169</v>
+        <v>0.1176425733402168</v>
       </c>
       <c r="G79">
-        <v>-8.977856356435709</v>
+        <v>-8.063526715581018</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.9366196983758336</v>
       </c>
       <c r="E80">
-        <v>-12.02189146451235</v>
+        <v>-11.84542588938145</v>
       </c>
       <c r="F80">
-        <v>0.3263560085241507</v>
+        <v>0.2730730148521482</v>
       </c>
       <c r="G80">
-        <v>-9.051906639058126</v>
+        <v>-8.344916465327991</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.5338508501757584</v>
       </c>
       <c r="E81">
-        <v>-13.83410524984989</v>
+        <v>-12.85406196205789</v>
       </c>
       <c r="F81">
-        <v>0.4913876671484338</v>
+        <v>-0.05729833319697086</v>
       </c>
       <c r="G81">
-        <v>-8.831937440701253</v>
+        <v>-6.954791909023704</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.100890422014257</v>
       </c>
       <c r="E82">
-        <v>-14.19531445059771</v>
+        <v>-13.41066575928867</v>
       </c>
       <c r="F82">
-        <v>0.3210014988240499</v>
+        <v>0.2829925568535032</v>
       </c>
       <c r="G82">
-        <v>-8.70748741278897</v>
+        <v>-7.478116326780615</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.3544259594233568</v>
       </c>
       <c r="E83">
-        <v>-14.77858643125966</v>
+        <v>-14.065600841122</v>
       </c>
       <c r="F83">
-        <v>0.2408691469146448</v>
+        <v>-0.09325083303631948</v>
       </c>
       <c r="G83">
-        <v>-8.172294689273773</v>
+        <v>-7.137001024959651</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.8212055391461873</v>
       </c>
       <c r="E84">
-        <v>-15.27053267660892</v>
+        <v>-16.56102097152276</v>
       </c>
       <c r="F84">
-        <v>0.04498848076351673</v>
+        <v>-0.03073087461251641</v>
       </c>
       <c r="G84">
-        <v>-8.549213541101954</v>
+        <v>-7.397610480356619</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.287940891482885</v>
       </c>
       <c r="E85">
-        <v>-15.82155286538824</v>
+        <v>-16.77101989668046</v>
       </c>
       <c r="F85">
-        <v>0.06260879277869602</v>
+        <v>0.3184343115351226</v>
       </c>
       <c r="G85">
-        <v>-8.425309753203651</v>
+        <v>-7.463636000591843</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.738581347808461</v>
       </c>
       <c r="E86">
-        <v>-17.57438024258919</v>
+        <v>-16.73144556232743</v>
       </c>
       <c r="F86">
-        <v>-0.1965995218131092</v>
+        <v>-0.09715229255900455</v>
       </c>
       <c r="G86">
-        <v>-7.760002658358478</v>
+        <v>-7.067777517733491</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.156261718040157</v>
       </c>
       <c r="E87">
-        <v>-19.17075789977315</v>
+        <v>-19.16601658748712</v>
       </c>
       <c r="F87">
-        <v>-0.4128070533889026</v>
+        <v>-0.3329090899549825</v>
       </c>
       <c r="G87">
-        <v>-7.191072165252567</v>
+        <v>-6.822005927443537</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.526654721107349</v>
       </c>
       <c r="E88">
-        <v>-20.66935674618348</v>
+        <v>-21.10892666116003</v>
       </c>
       <c r="F88">
-        <v>-0.1224583293818115</v>
+        <v>-0.4682977331070277</v>
       </c>
       <c r="G88">
-        <v>-7.127085941069534</v>
+        <v>-6.136242971711207</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.835650970439245</v>
       </c>
       <c r="E89">
-        <v>-21.8112341095876</v>
+        <v>-21.05823039464416</v>
       </c>
       <c r="F89">
-        <v>-0.2754934156966407</v>
+        <v>-0.49847049820798</v>
       </c>
       <c r="G89">
-        <v>-6.392959225553991</v>
+        <v>-6.645361838559105</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>3.071420386498594</v>
       </c>
       <c r="E90">
-        <v>-22.4536932455298</v>
+        <v>-23.71575630909749</v>
       </c>
       <c r="F90">
-        <v>-0.4407301642369732</v>
+        <v>-0.3676746022107092</v>
       </c>
       <c r="G90">
-        <v>-7.257187070217352</v>
+        <v>-6.399050629346251</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>3.225326849711225</v>
       </c>
       <c r="E91">
-        <v>-24.73722154863766</v>
+        <v>-24.76252666139252</v>
       </c>
       <c r="F91">
-        <v>-0.6153281984434682</v>
+        <v>-0.8169917667448234</v>
       </c>
       <c r="G91">
-        <v>-7.271720365134753</v>
+        <v>-6.209515276131897</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.292018123577953</v>
       </c>
       <c r="E92">
-        <v>-26.87200759448957</v>
+        <v>-27.31164543657624</v>
       </c>
       <c r="F92">
-        <v>-0.5608241675106619</v>
+        <v>-0.8706991936021637</v>
       </c>
       <c r="G92">
-        <v>-6.846560243708312</v>
+        <v>-5.426624224822889</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.270050797313778</v>
       </c>
       <c r="E93">
-        <v>-29.07601589402273</v>
+        <v>-28.5916412572143</v>
       </c>
       <c r="F93">
-        <v>-0.8334124215290574</v>
+        <v>-0.9151538186485489</v>
       </c>
       <c r="G93">
-        <v>-6.903309615342498</v>
+        <v>-5.936597212419919</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.16270295533773</v>
       </c>
       <c r="E94">
-        <v>-30.71052556658828</v>
+        <v>-30.56977153748187</v>
       </c>
       <c r="F94">
-        <v>-0.8571252502009322</v>
+        <v>-1.026784497510129</v>
       </c>
       <c r="G94">
-        <v>-6.966527792960421</v>
+        <v>-5.488332793674903</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.980288667429531</v>
       </c>
       <c r="E95">
-        <v>-33.16103002754396</v>
+        <v>-32.88706414279091</v>
       </c>
       <c r="F95">
-        <v>-0.8883583064122712</v>
+        <v>-0.9052960411778962</v>
       </c>
       <c r="G95">
-        <v>-6.86228202447431</v>
+        <v>-6.111168899796767</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.736283101404481</v>
       </c>
       <c r="E96">
-        <v>-35.17814594054356</v>
+        <v>-35.7545640757949</v>
       </c>
       <c r="F96">
-        <v>-0.843183095174361</v>
+        <v>-1.539805440639838</v>
       </c>
       <c r="G96">
-        <v>-7.133789795786559</v>
+        <v>-5.335700091586806</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.451691182005273</v>
       </c>
       <c r="E97">
-        <v>-36.93256507635821</v>
+        <v>-37.4471967122489</v>
       </c>
       <c r="F97">
-        <v>-1.352760269790946</v>
+        <v>-0.6585982114651048</v>
       </c>
       <c r="G97">
-        <v>-7.650801003200079</v>
+        <v>-5.78969175411476</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.143444124844093</v>
       </c>
       <c r="E98">
-        <v>-40.42764357971519</v>
+        <v>-39.90478144231557</v>
       </c>
       <c r="F98">
-        <v>-1.131674132142642</v>
+        <v>-1.459290623751854</v>
       </c>
       <c r="G98">
-        <v>-7.768957684042206</v>
+        <v>-6.251191733925781</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>1.841682212746466</v>
       </c>
       <c r="E99">
-        <v>-42.95053116920948</v>
+        <v>-43.07410190369378</v>
       </c>
       <c r="F99">
-        <v>-1.584649657341421</v>
+        <v>-0.9677257283645192</v>
       </c>
       <c r="G99">
-        <v>-7.605996079871582</v>
+        <v>-5.989757952689535</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.557182024984759</v>
       </c>
       <c r="E100">
-        <v>-45.54548715829883</v>
+        <v>-45.57123153303243</v>
       </c>
       <c r="F100">
-        <v>-1.288369162828051</v>
+        <v>-1.872275990879872</v>
       </c>
       <c r="G100">
-        <v>-8.156195506316296</v>
+        <v>-6.783663189007698</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.325487290575807</v>
       </c>
       <c r="E101">
-        <v>-46.90349952914104</v>
+        <v>-46.72038841840389</v>
       </c>
       <c r="F101">
-        <v>-1.460772972488705</v>
+        <v>-1.801930149674924</v>
       </c>
       <c r="G101">
-        <v>-8.118792962813611</v>
+        <v>-6.975876773563322</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.133449805579499</v>
       </c>
       <c r="E102">
-        <v>-49.85678121315382</v>
+        <v>-50.99982352649641</v>
       </c>
       <c r="F102">
-        <v>-1.821273533726102</v>
+        <v>-1.950263213126814</v>
       </c>
       <c r="G102">
-        <v>-8.204178553362492</v>
+        <v>-6.373039673044197</v>
       </c>
     </row>
   </sheetData>
